--- a/Visualization/generation_validation/generation_data_0.75.xlsx
+++ b/Visualization/generation_validation/generation_data_0.75.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Personal\博士论文\heatwave load forecasting\generation_data_proportion\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9060" activeTab="2"/>
+    <workbookView windowWidth="22188" windowHeight="9060"/>
   </bookViews>
   <sheets>
     <sheet name="欧洲" sheetId="1" r:id="rId1"/>
@@ -32,18 +37,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="88">
   <si>
     <t>Counrty</t>
   </si>
   <si>
-    <t>MLP</t>
-  </si>
-  <si>
     <t>LSTM</t>
-  </si>
-  <si>
-    <t>CNN</t>
   </si>
   <si>
     <t>MAE</t>
@@ -1265,477 +1264,233 @@
         <v>1</v>
       </c>
       <c r="C1" s="1"/>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
+      <c r="D1" s="1"/>
       <c r="E1" s="1"/>
-      <c r="F1" s="1" t="s">
-        <v>3</v>
-      </c>
+      <c r="F1" s="1"/>
       <c r="G1" s="1"/>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="1"/>
       <c r="B2" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>5</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B3">
-        <v>0.047678</v>
+        <v>0.042677</v>
       </c>
       <c r="C3">
-        <v>0.056333</v>
-      </c>
-      <c r="D3">
-        <v>0.042677</v>
-      </c>
-      <c r="E3">
         <v>0.053642</v>
-      </c>
-      <c r="F3">
-        <v>0.043848</v>
-      </c>
-      <c r="G3">
-        <v>0.058501</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B4">
-        <v>0.050599</v>
+        <v>0.046836</v>
       </c>
       <c r="C4">
-        <v>0.066585</v>
-      </c>
-      <c r="D4">
-        <v>0.046836</v>
-      </c>
-      <c r="E4">
         <v>0.057951</v>
-      </c>
-      <c r="F4">
-        <v>0.078168</v>
-      </c>
-      <c r="G4">
-        <v>0.091298</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B5">
-        <v>0.041456</v>
+        <v>0.037507</v>
       </c>
       <c r="C5">
-        <v>0.05677</v>
-      </c>
-      <c r="D5">
-        <v>0.037507</v>
-      </c>
-      <c r="E5">
         <v>0.046754</v>
-      </c>
-      <c r="F5">
-        <v>0.039617</v>
-      </c>
-      <c r="G5">
-        <v>0.049155</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B6">
-        <v>0.016931</v>
+        <v>0.035786</v>
       </c>
       <c r="C6">
-        <v>0.02082</v>
-      </c>
-      <c r="D6">
-        <v>0.035786</v>
-      </c>
-      <c r="E6">
         <v>0.047742</v>
-      </c>
-      <c r="F6">
-        <v>0.02142</v>
-      </c>
-      <c r="G6">
-        <v>0.027207</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B7">
-        <v>0.028421</v>
+        <v>0.023219</v>
       </c>
       <c r="C7">
-        <v>0.036332</v>
-      </c>
-      <c r="D7">
-        <v>0.023219</v>
-      </c>
-      <c r="E7">
         <v>0.028619</v>
-      </c>
-      <c r="F7">
-        <v>0.026472</v>
-      </c>
-      <c r="G7">
-        <v>0.032226</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B8">
-        <v>0.023715</v>
+        <v>0.026106</v>
       </c>
       <c r="C8">
-        <v>0.031226</v>
-      </c>
-      <c r="D8">
-        <v>0.026106</v>
-      </c>
-      <c r="E8">
         <v>0.031396</v>
-      </c>
-      <c r="F8">
-        <v>0.02618</v>
-      </c>
-      <c r="G8">
-        <v>0.033275</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B9">
-        <v>0.029487</v>
+        <v>0.024964</v>
       </c>
       <c r="C9">
-        <v>0.035804</v>
-      </c>
-      <c r="D9">
-        <v>0.024964</v>
-      </c>
-      <c r="E9">
         <v>0.033266</v>
-      </c>
-      <c r="F9">
-        <v>0.044944</v>
-      </c>
-      <c r="G9">
-        <v>0.050259</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B10">
-        <v>0.073734</v>
+        <v>0.040866</v>
       </c>
       <c r="C10">
-        <v>0.102914</v>
-      </c>
-      <c r="D10">
-        <v>0.040866</v>
-      </c>
-      <c r="E10">
         <v>0.048623</v>
-      </c>
-      <c r="F10">
-        <v>0.053016</v>
-      </c>
-      <c r="G10">
-        <v>0.069263</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B11">
-        <v>0.022309</v>
+        <v>0.022234</v>
       </c>
       <c r="C11">
-        <v>0.030024</v>
-      </c>
-      <c r="D11">
-        <v>0.022234</v>
-      </c>
-      <c r="E11">
         <v>0.028102</v>
-      </c>
-      <c r="F11">
-        <v>0.031912</v>
-      </c>
-      <c r="G11">
-        <v>0.041345</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B12">
-        <v>0.035076</v>
+        <v>0.029201</v>
       </c>
       <c r="C12">
-        <v>0.044214</v>
-      </c>
-      <c r="D12">
-        <v>0.029201</v>
-      </c>
-      <c r="E12">
         <v>0.037236</v>
-      </c>
-      <c r="F12">
-        <v>0.070231</v>
-      </c>
-      <c r="G12">
-        <v>0.079955</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B13">
-        <v>0.036954</v>
+        <v>0.031032</v>
       </c>
       <c r="C13">
-        <v>0.050122</v>
-      </c>
-      <c r="D13">
-        <v>0.031032</v>
-      </c>
-      <c r="E13">
         <v>0.040981</v>
-      </c>
-      <c r="F13">
-        <v>0.032568</v>
-      </c>
-      <c r="G13">
-        <v>0.043207</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B14">
-        <v>0.030635</v>
+        <v>0.028171</v>
       </c>
       <c r="C14">
-        <v>0.037968</v>
-      </c>
-      <c r="D14">
-        <v>0.028171</v>
-      </c>
-      <c r="E14">
         <v>0.039345</v>
-      </c>
-      <c r="F14">
-        <v>0.032233</v>
-      </c>
-      <c r="G14">
-        <v>0.045667</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B15">
-        <v>0.027632</v>
+        <v>0.026822</v>
       </c>
       <c r="C15">
-        <v>0.033672</v>
-      </c>
-      <c r="D15">
-        <v>0.026822</v>
-      </c>
-      <c r="E15">
         <v>0.032567</v>
-      </c>
-      <c r="F15">
-        <v>0.031615</v>
-      </c>
-      <c r="G15">
-        <v>0.039165</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16">
+        <v>0.033569</v>
+      </c>
+      <c r="C16">
+        <v>0.063012</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17">
+        <v>0.032841</v>
+      </c>
+      <c r="C17">
+        <v>0.043839</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
         <v>19</v>
       </c>
-      <c r="B16">
-        <v>0.018618</v>
-      </c>
-      <c r="C16">
-        <v>0.022758</v>
-      </c>
-      <c r="D16">
-        <v>0.033569</v>
-      </c>
-      <c r="E16">
-        <v>0.063012</v>
-      </c>
-      <c r="F16">
-        <v>0.021346</v>
-      </c>
-      <c r="G16">
-        <v>0.026968</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17" t="s">
+      <c r="B18">
+        <v>0.032944</v>
+      </c>
+      <c r="C18">
+        <v>0.045729</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
         <v>20</v>
       </c>
-      <c r="B17">
-        <v>0.025031</v>
-      </c>
-      <c r="C17">
-        <v>0.030818</v>
-      </c>
-      <c r="D17">
-        <v>0.032841</v>
-      </c>
-      <c r="E17">
-        <v>0.043839</v>
-      </c>
-      <c r="F17">
-        <v>0.045193</v>
-      </c>
-      <c r="G17">
-        <v>0.052552</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18" t="s">
+      <c r="B19">
+        <v>0.030924</v>
+      </c>
+      <c r="C19">
+        <v>0.040856</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
         <v>21</v>
       </c>
-      <c r="B18">
-        <v>0.041428</v>
-      </c>
-      <c r="C18">
-        <v>0.05628</v>
-      </c>
-      <c r="D18">
-        <v>0.032944</v>
-      </c>
-      <c r="E18">
-        <v>0.045729</v>
-      </c>
-      <c r="F18">
-        <v>0.057991</v>
-      </c>
-      <c r="G18">
-        <v>0.071237</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19" t="s">
+      <c r="B20">
+        <v>0.038992</v>
+      </c>
+      <c r="C20">
+        <v>0.051807</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B19">
-        <v>0.026594</v>
-      </c>
-      <c r="C19">
-        <v>0.035627</v>
-      </c>
-      <c r="D19">
-        <v>0.030924</v>
-      </c>
-      <c r="E19">
-        <v>0.040856</v>
-      </c>
-      <c r="F19">
-        <v>0.049025</v>
-      </c>
-      <c r="G19">
-        <v>0.060435</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20" t="s">
-        <v>23</v>
-      </c>
-      <c r="B20">
-        <v>0.042423</v>
-      </c>
-      <c r="C20">
-        <v>0.052023</v>
-      </c>
-      <c r="D20">
-        <v>0.038992</v>
-      </c>
-      <c r="E20">
-        <v>0.051807</v>
-      </c>
-      <c r="F20">
-        <v>0.042462</v>
-      </c>
-      <c r="G20">
-        <v>0.0541</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21" s="2" t="s">
-        <v>24</v>
-      </c>
       <c r="B21">
-        <f>AVERAGE(B3:B20)</f>
-        <v>0.0343733888888889</v>
+        <f xml:space="preserve">AVERAGE(B3:B20)</f>
+        <v>0.0324828333333333</v>
       </c>
       <c r="C21">
-        <f t="shared" ref="B21:G21" si="0">AVERAGE(C3:C20)</f>
-        <v>0.0444605555555556</v>
-      </c>
-      <c r="D21">
-        <f t="shared" si="0"/>
-        <v>0.0324828333333333</v>
-      </c>
-      <c r="E21">
-        <f t="shared" si="0"/>
+        <f xml:space="preserve">AVERAGE(C3:C20)</f>
         <v>0.0428592777777778</v>
-      </c>
-      <c r="F21">
-        <f t="shared" si="0"/>
-        <v>0.0415689444444444</v>
-      </c>
-      <c r="G21">
-        <f t="shared" si="0"/>
-        <v>0.0514341666666667</v>
       </c>
     </row>
   </sheetData>
@@ -1762,552 +1517,272 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1"/>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
+      <c r="D1" s="1"/>
       <c r="E1" s="1"/>
-      <c r="F1" s="1" t="s">
-        <v>3</v>
-      </c>
+      <c r="F1" s="1"/>
       <c r="G1" s="1"/>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="1"/>
       <c r="B2" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>5</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B3">
-        <v>0.02585</v>
+        <v>0.021835</v>
       </c>
       <c r="C3">
-        <v>0.034232</v>
-      </c>
-      <c r="D3">
-        <v>0.021835</v>
-      </c>
-      <c r="E3">
         <v>0.02871</v>
-      </c>
-      <c r="F3">
-        <v>0.029251</v>
-      </c>
-      <c r="G3">
-        <v>0.034851</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B4">
-        <v>0.016643</v>
+        <v>0.03127</v>
       </c>
       <c r="C4">
-        <v>0.022538</v>
-      </c>
-      <c r="D4">
-        <v>0.03127</v>
-      </c>
-      <c r="E4">
         <v>0.04587</v>
-      </c>
-      <c r="F4">
-        <v>0.022658</v>
-      </c>
-      <c r="G4">
-        <v>0.028121</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B5">
-        <v>0.022008</v>
+        <v>0.020086</v>
       </c>
       <c r="C5">
-        <v>0.028692</v>
-      </c>
-      <c r="D5">
-        <v>0.020086</v>
-      </c>
-      <c r="E5">
         <v>0.027574</v>
-      </c>
-      <c r="F5">
-        <v>0.027038</v>
-      </c>
-      <c r="G5">
-        <v>0.031634</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B6">
-        <v>0.02086</v>
+        <v>0.02286</v>
       </c>
       <c r="C6">
-        <v>0.027024</v>
-      </c>
-      <c r="D6">
-        <v>0.02286</v>
-      </c>
-      <c r="E6">
         <v>0.034042</v>
-      </c>
-      <c r="F6">
-        <v>0.02449</v>
-      </c>
-      <c r="G6">
-        <v>0.030866</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B7">
-        <v>0.050502</v>
+        <v>0.042179</v>
       </c>
       <c r="C7">
-        <v>0.065406</v>
-      </c>
-      <c r="D7">
-        <v>0.042179</v>
-      </c>
-      <c r="E7">
         <v>0.050375</v>
-      </c>
-      <c r="F7">
-        <v>0.068182</v>
-      </c>
-      <c r="G7">
-        <v>0.078582</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B8">
-        <v>0.027112</v>
+        <v>0.025471</v>
       </c>
       <c r="C8">
-        <v>0.040769</v>
-      </c>
-      <c r="D8">
-        <v>0.025471</v>
-      </c>
-      <c r="E8">
         <v>0.039255</v>
-      </c>
-      <c r="F8">
-        <v>0.033418</v>
-      </c>
-      <c r="G8">
-        <v>0.039574</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B9">
-        <v>0.024403</v>
+        <v>0.024909</v>
       </c>
       <c r="C9">
-        <v>0.031045</v>
-      </c>
-      <c r="D9">
-        <v>0.024909</v>
-      </c>
-      <c r="E9">
         <v>0.035536</v>
-      </c>
-      <c r="F9">
-        <v>0.028741</v>
-      </c>
-      <c r="G9">
-        <v>0.036462</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B10">
-        <v>0.21046</v>
+        <v>0.044113</v>
       </c>
       <c r="C10">
-        <v>0.267755</v>
-      </c>
-      <c r="D10">
-        <v>0.044113</v>
-      </c>
-      <c r="E10">
         <v>0.050875</v>
-      </c>
-      <c r="F10">
-        <v>0.086682</v>
-      </c>
-      <c r="G10">
-        <v>0.091648</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B11">
-        <v>0.032438</v>
+        <v>0.030082</v>
       </c>
       <c r="C11">
-        <v>0.050092</v>
-      </c>
-      <c r="D11">
-        <v>0.030082</v>
-      </c>
-      <c r="E11">
         <v>0.046624</v>
-      </c>
-      <c r="F11">
-        <v>0.037723</v>
-      </c>
-      <c r="G11">
-        <v>0.049992</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B12">
-        <v>0.029986</v>
+        <v>0.029574</v>
       </c>
       <c r="C12">
-        <v>0.038181</v>
-      </c>
-      <c r="D12">
-        <v>0.029574</v>
-      </c>
-      <c r="E12">
         <v>0.037147</v>
-      </c>
-      <c r="F12">
-        <v>0.047564</v>
-      </c>
-      <c r="G12">
-        <v>0.054946</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B13">
-        <v>0.058372</v>
+        <v>0.032019</v>
       </c>
       <c r="C13">
-        <v>0.073859</v>
-      </c>
-      <c r="D13">
-        <v>0.032019</v>
-      </c>
-      <c r="E13">
         <v>0.043187</v>
-      </c>
-      <c r="F13">
-        <v>0.057128</v>
-      </c>
-      <c r="G13">
-        <v>0.06603</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B14">
-        <v>0.024403</v>
+        <v>0.019499</v>
       </c>
       <c r="C14">
-        <v>0.034953</v>
-      </c>
-      <c r="D14">
-        <v>0.019499</v>
-      </c>
-      <c r="E14">
         <v>0.028323</v>
-      </c>
-      <c r="F14">
-        <v>0.025717</v>
-      </c>
-      <c r="G14">
-        <v>0.032652</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B15">
-        <v>0.030377</v>
+        <v>0.02871</v>
       </c>
       <c r="C15">
-        <v>0.045138</v>
-      </c>
-      <c r="D15">
-        <v>0.02871</v>
-      </c>
-      <c r="E15">
         <v>0.038071</v>
-      </c>
-      <c r="F15">
-        <v>0.037977</v>
-      </c>
-      <c r="G15">
-        <v>0.04815</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16">
+        <v>0.037778</v>
+      </c>
+      <c r="C16">
+        <v>0.048715</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17">
+        <v>0.01552</v>
+      </c>
+      <c r="C17">
+        <v>0.023329</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
         <v>39</v>
       </c>
-      <c r="B16">
-        <v>0.043783</v>
-      </c>
-      <c r="C16">
-        <v>0.0565</v>
-      </c>
-      <c r="D16">
-        <v>0.037778</v>
-      </c>
-      <c r="E16">
-        <v>0.048715</v>
-      </c>
-      <c r="F16">
-        <v>0.046634</v>
-      </c>
-      <c r="G16">
-        <v>0.057816</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17" t="s">
+      <c r="B18">
+        <v>0.055465</v>
+      </c>
+      <c r="C18">
+        <v>0.067959</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
         <v>40</v>
       </c>
-      <c r="B17">
-        <v>0.017707</v>
-      </c>
-      <c r="C17">
-        <v>0.026166</v>
-      </c>
-      <c r="D17">
-        <v>0.01552</v>
-      </c>
-      <c r="E17">
-        <v>0.023329</v>
-      </c>
-      <c r="F17">
-        <v>0.020594</v>
-      </c>
-      <c r="G17">
-        <v>0.027627</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18" t="s">
+      <c r="B19">
+        <v>0.059069</v>
+      </c>
+      <c r="C19">
+        <v>0.072188</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
         <v>41</v>
       </c>
-      <c r="B18">
-        <v>0.095797</v>
-      </c>
-      <c r="C18">
-        <v>0.114577</v>
-      </c>
-      <c r="D18">
-        <v>0.055465</v>
-      </c>
-      <c r="E18">
-        <v>0.067959</v>
-      </c>
-      <c r="F18">
-        <v>0.099059</v>
-      </c>
-      <c r="G18">
-        <v>0.109836</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19" t="s">
+      <c r="B20">
+        <v>0.035414</v>
+      </c>
+      <c r="C20">
+        <v>0.057194</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
         <v>42</v>
       </c>
-      <c r="B19">
-        <v>0.258667</v>
-      </c>
-      <c r="C19">
-        <v>0.323066</v>
-      </c>
-      <c r="D19">
-        <v>0.059069</v>
-      </c>
-      <c r="E19">
-        <v>0.072188</v>
-      </c>
-      <c r="F19">
-        <v>0.1432</v>
-      </c>
-      <c r="G19">
-        <v>0.157716</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20" t="s">
+      <c r="B21">
+        <v>0.023252</v>
+      </c>
+      <c r="C21">
+        <v>0.027737</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
         <v>43</v>
       </c>
-      <c r="B20">
-        <v>0.040628</v>
-      </c>
-      <c r="C20">
-        <v>0.065182</v>
-      </c>
-      <c r="D20">
-        <v>0.035414</v>
-      </c>
-      <c r="E20">
-        <v>0.057194</v>
-      </c>
-      <c r="F20">
-        <v>0.042555</v>
-      </c>
-      <c r="G20">
-        <v>0.065174</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21" t="s">
+      <c r="B22">
+        <v>0.022349</v>
+      </c>
+      <c r="C22">
+        <v>0.030657</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" t="s">
         <v>44</v>
       </c>
-      <c r="B21">
-        <v>0.027541</v>
-      </c>
-      <c r="C21">
-        <v>0.035398</v>
-      </c>
-      <c r="D21">
-        <v>0.023252</v>
-      </c>
-      <c r="E21">
-        <v>0.027737</v>
-      </c>
-      <c r="F21">
-        <v>0.04684</v>
-      </c>
-      <c r="G21">
-        <v>0.05209</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22" t="s">
-        <v>45</v>
-      </c>
-      <c r="B22">
-        <v>0.020973</v>
-      </c>
-      <c r="C22">
-        <v>0.026628</v>
-      </c>
-      <c r="D22">
-        <v>0.022349</v>
-      </c>
-      <c r="E22">
-        <v>0.030657</v>
-      </c>
-      <c r="F22">
-        <v>0.029139</v>
-      </c>
-      <c r="G22">
-        <v>0.036761</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23" t="s">
-        <v>46</v>
-      </c>
       <c r="B23">
-        <v>0.057893</v>
+        <v>0.032655</v>
       </c>
       <c r="C23">
-        <v>0.082928</v>
-      </c>
-      <c r="D23">
-        <v>0.032655</v>
-      </c>
-      <c r="E23">
         <v>0.039475</v>
       </c>
-      <c r="F23">
-        <v>0.051468</v>
-      </c>
-      <c r="G23">
-        <v>0.056319</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
+    </row>
+    <row r="24" spans="1:3">
       <c r="A24" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B24">
-        <f t="shared" ref="B24:G24" si="0">AVERAGE(B3:B23)</f>
-        <v>0.0541144285714286</v>
+        <f xml:space="preserve">AVERAGE(B3:B23)</f>
+        <v>0.0311480476190476</v>
       </c>
       <c r="C24">
-        <f t="shared" si="0"/>
-        <v>0.0709585238095238</v>
-      </c>
-      <c r="D24">
-        <f t="shared" si="0"/>
-        <v>0.0311480476190476</v>
-      </c>
-      <c r="E24">
-        <f t="shared" si="0"/>
+        <f xml:space="preserve">AVERAGE(C3:C23)</f>
         <v>0.0415639523809524</v>
-      </c>
-      <c r="F24">
-        <f t="shared" si="0"/>
-        <v>0.0479075238095238</v>
-      </c>
-      <c r="G24">
-        <f t="shared" si="0"/>
-        <v>0.0565165238095238</v>
       </c>
     </row>
   </sheetData>
@@ -2331,121 +1806,70 @@
   <cols>
     <col min="2" max="3" width="10.6666666666667"/>
     <col min="4" max="4" width="9.66666666666667"/>
-    <col min="5" max="6" width="10.6666666666667"/>
+    <col min="5" max="5" width="12.8888888888889"/>
+    <col min="6" max="6" width="10.6666666666667"/>
     <col min="7" max="7" width="9.66666666666667"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1"/>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
+      <c r="D1" s="1"/>
       <c r="E1" s="1"/>
-      <c r="F1" s="1" t="s">
-        <v>3</v>
-      </c>
+      <c r="F1" s="1"/>
       <c r="G1" s="1"/>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="1"/>
       <c r="B2" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>5</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B3">
-        <v>0.031736</v>
+        <v>0.041494336</v>
       </c>
       <c r="C3">
-        <v>0.038754</v>
-      </c>
-      <c r="D3">
-        <v>0.042352</v>
-      </c>
-      <c r="E3">
-        <v>0.052154</v>
-      </c>
-      <c r="F3">
-        <v>0.043688</v>
-      </c>
-      <c r="G3">
-        <v>0.052643</v>
+        <v>0.050015914269</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B4">
-        <v>0.021363</v>
+        <v>0.026196608</v>
       </c>
       <c r="C4">
-        <v>0.028334</v>
-      </c>
-      <c r="D4">
-        <v>0.022311</v>
-      </c>
-      <c r="E4">
-        <v>0.029529</v>
-      </c>
-      <c r="F4">
-        <v>0.029206</v>
-      </c>
-      <c r="G4">
-        <v>0.035735</v>
+        <v>0.0358479487</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B5">
-        <f t="shared" ref="B5:G5" si="0">AVERAGE(B3:B4)</f>
-        <v>0.0265495</v>
+        <f xml:space="preserve">AVERAGE(B3:B4)</f>
+        <v>0.033845472</v>
       </c>
       <c r="C5">
-        <f t="shared" si="0"/>
-        <v>0.033544</v>
-      </c>
-      <c r="D5">
-        <f t="shared" si="0"/>
-        <v>0.0323315</v>
-      </c>
-      <c r="E5">
-        <f t="shared" si="0"/>
-        <v>0.0408415</v>
-      </c>
-      <c r="F5">
-        <f t="shared" si="0"/>
-        <v>0.036447</v>
-      </c>
-      <c r="G5">
-        <f t="shared" si="0"/>
-        <v>0.044189</v>
+        <f xml:space="preserve">AVERAGE(C3:C4)</f>
+        <v>0.0429319314845</v>
       </c>
     </row>
   </sheetData>
@@ -2476,253 +1900,129 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1"/>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
+      <c r="D1" s="1"/>
       <c r="E1" s="1"/>
-      <c r="F1" s="1" t="s">
-        <v>3</v>
-      </c>
+      <c r="F1" s="1"/>
       <c r="G1" s="1"/>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="1"/>
       <c r="B2" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>5</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B3">
-        <v>0.044542</v>
+        <v>0.029083</v>
       </c>
       <c r="C3">
-        <v>0.059457</v>
-      </c>
-      <c r="D3">
-        <v>0.035628</v>
-      </c>
-      <c r="E3">
-        <v>0.047139</v>
-      </c>
-      <c r="F3">
-        <v>0.037845</v>
-      </c>
-      <c r="G3">
-        <v>0.048607</v>
+        <v>0.037234</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B4">
-        <v>0.052626</v>
+        <v>0.032468</v>
       </c>
       <c r="C4">
-        <v>0.065856</v>
-      </c>
-      <c r="D4">
-        <v>0.032301</v>
-      </c>
-      <c r="E4">
-        <v>0.04053</v>
-      </c>
-      <c r="F4">
-        <v>0.045505</v>
-      </c>
-      <c r="G4">
-        <v>0.058218</v>
+        <v>0.040697</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B5">
-        <v>0.041069</v>
+        <v>0.034083</v>
       </c>
       <c r="C5">
-        <v>0.054672</v>
-      </c>
-      <c r="D5">
-        <v>0.033634</v>
-      </c>
-      <c r="E5">
-        <v>0.039373</v>
-      </c>
-      <c r="F5">
-        <v>0.083671</v>
-      </c>
-      <c r="G5">
-        <v>0.090164</v>
+        <v>0.039919</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B6">
-        <v>0.04537</v>
+        <v>0.036018</v>
       </c>
       <c r="C6">
-        <v>0.060382</v>
-      </c>
-      <c r="D6">
-        <v>0.035648</v>
-      </c>
-      <c r="E6">
-        <v>0.045168</v>
-      </c>
-      <c r="F6">
-        <v>0.036796</v>
-      </c>
-      <c r="G6">
-        <v>0.048423</v>
+        <v>0.045451</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B7">
-        <v>0.057801</v>
+        <v>0.041105</v>
       </c>
       <c r="C7">
-        <v>0.075216</v>
-      </c>
-      <c r="D7">
-        <v>0.039957</v>
-      </c>
-      <c r="E7">
-        <v>0.053087</v>
-      </c>
-      <c r="F7">
-        <v>0.046717</v>
-      </c>
-      <c r="G7">
-        <v>0.060976</v>
+        <v>0.050968</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B8">
-        <v>0.04318</v>
+        <v>0.032601</v>
       </c>
       <c r="C8">
-        <v>0.057788</v>
-      </c>
-      <c r="D8">
-        <v>0.033369</v>
-      </c>
-      <c r="E8">
-        <v>0.045369</v>
-      </c>
-      <c r="F8">
-        <v>0.036472</v>
-      </c>
-      <c r="G8">
-        <v>0.047767</v>
+        <v>0.04435</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B9">
-        <v>0.053301</v>
+        <v>0.045313</v>
       </c>
       <c r="C9">
-        <v>0.066625</v>
-      </c>
-      <c r="D9">
-        <v>0.040016</v>
-      </c>
-      <c r="E9">
-        <v>0.053645</v>
-      </c>
-      <c r="F9">
-        <v>0.046634</v>
-      </c>
-      <c r="G9">
-        <v>0.059967</v>
+        <v>0.059344</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B10">
-        <v>0.053111</v>
+        <v>0.036214</v>
       </c>
       <c r="C10">
-        <v>0.067747</v>
-      </c>
-      <c r="D10">
-        <v>0.039322</v>
-      </c>
-      <c r="E10">
-        <v>0.049735</v>
-      </c>
-      <c r="F10">
-        <v>0.060859</v>
-      </c>
-      <c r="G10">
-        <v>0.072098</v>
+        <v>0.047988</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B11">
-        <f t="shared" ref="B11:G11" si="0">AVERAGE(B3:B10)</f>
-        <v>0.048875</v>
+        <f xml:space="preserve">AVERAGE(B3:B10)</f>
+        <v>0.035860625</v>
       </c>
       <c r="C11">
-        <f t="shared" si="0"/>
-        <v>0.063467875</v>
-      </c>
-      <c r="D11">
-        <f t="shared" si="0"/>
-        <v>0.036234375</v>
-      </c>
-      <c r="E11">
-        <f t="shared" si="0"/>
-        <v>0.04675575</v>
-      </c>
-      <c r="F11">
-        <f t="shared" si="0"/>
-        <v>0.049312375</v>
-      </c>
-      <c r="G11">
-        <f t="shared" si="0"/>
-        <v>0.0607775</v>
+        <f xml:space="preserve">AVERAGE(C3:C10)</f>
+        <v>0.045743875</v>
       </c>
     </row>
   </sheetData>
@@ -2749,506 +2049,250 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1"/>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
+      <c r="D1" s="1"/>
       <c r="E1" s="1"/>
-      <c r="F1" s="1" t="s">
-        <v>3</v>
-      </c>
+      <c r="F1" s="1"/>
       <c r="G1" s="1"/>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="1"/>
       <c r="B2" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>5</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B3">
-        <v>0.040808</v>
+        <v>0.042066</v>
       </c>
       <c r="C3">
-        <v>0.053783</v>
-      </c>
-      <c r="D3">
-        <v>0.042156</v>
-      </c>
-      <c r="E3">
-        <v>0.05733</v>
-      </c>
-      <c r="F3">
-        <v>0.042571</v>
-      </c>
-      <c r="G3">
-        <v>0.061383</v>
+        <v>0.059758</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B4">
-        <v>0.028073</v>
+        <v>0.018232</v>
       </c>
       <c r="C4">
-        <v>0.039289</v>
-      </c>
-      <c r="D4">
-        <v>0.020538</v>
-      </c>
-      <c r="E4">
-        <v>0.031033</v>
-      </c>
-      <c r="F4">
-        <v>0.019544</v>
-      </c>
-      <c r="G4">
-        <v>0.027048</v>
+        <v>0.02705</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B5">
-        <v>0.042842</v>
+        <v>0.027142</v>
       </c>
       <c r="C5">
-        <v>0.059794</v>
-      </c>
-      <c r="D5">
-        <v>0.026129</v>
-      </c>
-      <c r="E5">
-        <v>0.035433</v>
-      </c>
-      <c r="F5">
-        <v>0.041292</v>
-      </c>
-      <c r="G5">
-        <v>0.053557</v>
+        <v>0.035624</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B6">
-        <v>0.051323</v>
+        <v>0.037005</v>
       </c>
       <c r="C6">
-        <v>0.073131</v>
-      </c>
-      <c r="D6">
-        <v>0.038768</v>
-      </c>
-      <c r="E6">
-        <v>0.059571</v>
-      </c>
-      <c r="F6">
-        <v>0.045748</v>
-      </c>
-      <c r="G6">
-        <v>0.060918</v>
+        <v>0.050779</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B7">
-        <v>0.037025</v>
+        <v>0.029156</v>
       </c>
       <c r="C7">
-        <v>0.049127</v>
-      </c>
-      <c r="D7">
-        <v>0.024962</v>
-      </c>
-      <c r="E7">
-        <v>0.035498</v>
-      </c>
-      <c r="F7">
-        <v>0.02415</v>
-      </c>
-      <c r="G7">
-        <v>0.032512</v>
+        <v>0.042744</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B8">
-        <v>0.053735</v>
+        <v>0.057054</v>
       </c>
       <c r="C8">
-        <v>0.077568</v>
-      </c>
-      <c r="D8">
-        <v>0.046712</v>
-      </c>
-      <c r="E8">
-        <v>0.068398</v>
-      </c>
-      <c r="F8">
-        <v>0.055099</v>
-      </c>
-      <c r="G8">
-        <v>0.072401</v>
+        <v>0.081802</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B9">
-        <v>0.043207</v>
+        <v>0.024282</v>
       </c>
       <c r="C9">
-        <v>0.06185</v>
-      </c>
-      <c r="D9">
-        <v>0.028476</v>
-      </c>
-      <c r="E9">
-        <v>0.037953</v>
-      </c>
-      <c r="F9">
-        <v>0.035142</v>
-      </c>
-      <c r="G9">
-        <v>0.043383</v>
+        <v>0.03338</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B10">
-        <v>0.024188</v>
+        <v>0.026555</v>
       </c>
       <c r="C10">
-        <v>0.031338</v>
-      </c>
-      <c r="D10">
-        <v>0.015354</v>
-      </c>
-      <c r="E10">
-        <v>0.01993</v>
-      </c>
-      <c r="F10">
-        <v>0.020183</v>
-      </c>
-      <c r="G10">
-        <v>0.025551</v>
+        <v>0.034977</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B11">
-        <v>0.054459</v>
+        <v>0.058687</v>
       </c>
       <c r="C11">
-        <v>0.077109</v>
-      </c>
-      <c r="D11">
-        <v>0.045647</v>
-      </c>
-      <c r="E11">
-        <v>0.066318</v>
-      </c>
-      <c r="F11">
-        <v>0.047234</v>
-      </c>
-      <c r="G11">
-        <v>0.066439</v>
+        <v>0.082185</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B12">
-        <v>0.044353</v>
+        <v>0.054275</v>
       </c>
       <c r="C12">
-        <v>0.06288</v>
-      </c>
-      <c r="D12">
-        <v>0.043125</v>
-      </c>
-      <c r="E12">
-        <v>0.059235</v>
-      </c>
-      <c r="F12">
-        <v>0.049337</v>
-      </c>
-      <c r="G12">
-        <v>0.066018</v>
+        <v>0.076646</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B13">
-        <v>0.034714</v>
+        <v>0.034901</v>
       </c>
       <c r="C13">
-        <v>0.043133</v>
-      </c>
-      <c r="D13">
-        <v>0.028371</v>
-      </c>
-      <c r="E13">
-        <v>0.037049</v>
-      </c>
-      <c r="F13">
-        <v>0.028203</v>
-      </c>
-      <c r="G13">
-        <v>0.037041</v>
+        <v>0.044635</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B14">
-        <v>0.054722</v>
+        <v>0.049948</v>
       </c>
       <c r="C14">
-        <v>0.068753</v>
-      </c>
-      <c r="D14">
-        <v>0.044121</v>
-      </c>
-      <c r="E14">
-        <v>0.056924</v>
-      </c>
-      <c r="F14">
-        <v>0.049222</v>
-      </c>
-      <c r="G14">
-        <v>0.061819</v>
+        <v>0.073251</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B15">
-        <v>0.040608</v>
+        <v>0.03288</v>
       </c>
       <c r="C15">
-        <v>0.057795</v>
-      </c>
-      <c r="D15">
-        <v>0.028591</v>
-      </c>
-      <c r="E15">
-        <v>0.041303</v>
-      </c>
-      <c r="F15">
-        <v>0.044988</v>
-      </c>
-      <c r="G15">
-        <v>0.058089</v>
+        <v>0.043872</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
+        <v>68</v>
+      </c>
+      <c r="B16">
+        <v>0.043059</v>
+      </c>
+      <c r="C16">
+        <v>0.057434</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>69</v>
+      </c>
+      <c r="B17">
+        <v>0.058158</v>
+      </c>
+      <c r="C17">
+        <v>0.077158</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
         <v>70</v>
       </c>
-      <c r="B16">
-        <v>0.051576</v>
-      </c>
-      <c r="C16">
-        <v>0.073173</v>
-      </c>
-      <c r="D16">
-        <v>0.041215</v>
-      </c>
-      <c r="E16">
-        <v>0.053434</v>
-      </c>
-      <c r="F16">
-        <v>0.043466</v>
-      </c>
-      <c r="G16">
-        <v>0.057757</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17" t="s">
+      <c r="B18">
+        <v>0.031584</v>
+      </c>
+      <c r="C18">
+        <v>0.041509</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
         <v>71</v>
       </c>
-      <c r="B17">
-        <v>0.057269</v>
-      </c>
-      <c r="C17">
-        <v>0.078193</v>
-      </c>
-      <c r="D17">
-        <v>0.05665</v>
-      </c>
-      <c r="E17">
-        <v>0.078006</v>
-      </c>
-      <c r="F17">
-        <v>0.053564</v>
-      </c>
-      <c r="G17">
-        <v>0.070649</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18" t="s">
+      <c r="B19">
+        <v>0.046945</v>
+      </c>
+      <c r="C19">
+        <v>0.062618</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
         <v>72</v>
       </c>
-      <c r="B18">
-        <v>0.047983</v>
-      </c>
-      <c r="C18">
-        <v>0.062118</v>
-      </c>
-      <c r="D18">
-        <v>0.02157</v>
-      </c>
-      <c r="E18">
-        <v>0.028893</v>
-      </c>
-      <c r="F18">
-        <v>0.048195</v>
-      </c>
-      <c r="G18">
-        <v>0.065512</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19" t="s">
+      <c r="B20">
+        <v>0.041746</v>
+      </c>
+      <c r="C20">
+        <v>0.054405</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
         <v>73</v>
       </c>
-      <c r="B19">
-        <v>0.048405</v>
-      </c>
-      <c r="C19">
-        <v>0.067409</v>
-      </c>
-      <c r="D19">
-        <v>0.037153</v>
-      </c>
-      <c r="E19">
-        <v>0.05213</v>
-      </c>
-      <c r="F19">
-        <v>0.043345</v>
-      </c>
-      <c r="G19">
-        <v>0.060061</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20" t="s">
-        <v>74</v>
-      </c>
-      <c r="B20">
-        <v>0.044262</v>
-      </c>
-      <c r="C20">
-        <v>0.060222</v>
-      </c>
-      <c r="D20">
-        <v>0.035643</v>
-      </c>
-      <c r="E20">
-        <v>0.04929</v>
-      </c>
-      <c r="F20">
-        <v>0.043306</v>
-      </c>
-      <c r="G20">
-        <v>0.056596</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21" t="s">
-        <v>75</v>
-      </c>
       <c r="B21">
-        <v>0.047076</v>
+        <v>0.031539</v>
       </c>
       <c r="C21">
-        <v>0.065504</v>
-      </c>
-      <c r="D21">
-        <v>0.028233</v>
-      </c>
-      <c r="E21">
-        <v>0.037404</v>
-      </c>
-      <c r="F21">
-        <v>0.043315</v>
-      </c>
-      <c r="G21">
-        <v>0.058671</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
+        <v>0.044812</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
       <c r="A22" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B22">
-        <f t="shared" ref="B22:G22" si="0">AVERAGE(B3:B21)</f>
-        <v>0.0445593684210526</v>
+        <f xml:space="preserve">AVERAGE(B3:B21)</f>
+        <v>0.0392217894736842</v>
       </c>
       <c r="C22">
-        <f t="shared" si="0"/>
-        <v>0.0611667894736842</v>
-      </c>
-      <c r="D22">
-        <f t="shared" si="0"/>
-        <v>0.0343902105263158</v>
-      </c>
-      <c r="E22">
-        <f t="shared" si="0"/>
-        <v>0.0476385263157895</v>
-      </c>
-      <c r="F22">
-        <f t="shared" si="0"/>
-        <v>0.0409423157894737</v>
-      </c>
-      <c r="G22">
-        <f t="shared" si="0"/>
-        <v>0.054495</v>
+        <f xml:space="preserve">AVERAGE(C3:C21)</f>
+        <v>0.0539283684210526</v>
       </c>
     </row>
   </sheetData>
@@ -3280,388 +2324,192 @@
         <v>1</v>
       </c>
       <c r="C1" s="1"/>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
+      <c r="D1" s="1"/>
       <c r="E1" s="1"/>
-      <c r="F1" s="1" t="s">
-        <v>3</v>
-      </c>
+      <c r="F1" s="1"/>
       <c r="G1" s="1"/>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="1"/>
       <c r="B2" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>5</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B3">
-        <v>0.095737</v>
+        <v>0.058498</v>
       </c>
       <c r="C3">
-        <v>0.123396</v>
-      </c>
-      <c r="D3">
-        <v>0.063896</v>
-      </c>
-      <c r="E3">
-        <v>0.082274</v>
-      </c>
-      <c r="F3">
-        <v>0.117125</v>
-      </c>
-      <c r="G3">
-        <v>0.130095</v>
+        <v>0.071699</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B4">
-        <v>0.034417</v>
+        <v>0.018768</v>
       </c>
       <c r="C4">
-        <v>0.045804</v>
-      </c>
-      <c r="D4">
-        <v>0.017415</v>
-      </c>
-      <c r="E4">
-        <v>0.022979</v>
-      </c>
-      <c r="F4">
-        <v>0.033682</v>
-      </c>
-      <c r="G4">
-        <v>0.042553</v>
+        <v>0.024052</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B5">
-        <v>0.062468</v>
+        <v>0.0271</v>
       </c>
       <c r="C5">
-        <v>0.089747</v>
-      </c>
-      <c r="D5">
-        <v>0.021192</v>
-      </c>
-      <c r="E5">
-        <v>0.027142</v>
-      </c>
-      <c r="F5">
-        <v>0.027576</v>
-      </c>
-      <c r="G5">
-        <v>0.033987</v>
+        <v>0.033807</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B6">
-        <v>0.048639</v>
+        <v>0.029151</v>
       </c>
       <c r="C6">
-        <v>0.05689</v>
-      </c>
-      <c r="D6">
-        <v>0.029307</v>
-      </c>
-      <c r="E6">
-        <v>0.036756</v>
-      </c>
-      <c r="F6">
-        <v>0.045881</v>
-      </c>
-      <c r="G6">
-        <v>0.052942</v>
+        <v>0.037965</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B7">
-        <v>0.039883</v>
+        <v>0.03131</v>
       </c>
       <c r="C7">
-        <v>0.053642</v>
-      </c>
-      <c r="D7">
-        <v>0.03071</v>
-      </c>
-      <c r="E7">
-        <v>0.038702</v>
-      </c>
-      <c r="F7">
-        <v>0.040675</v>
-      </c>
-      <c r="G7">
-        <v>0.049606</v>
+        <v>0.039556</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B8">
-        <v>0.031794</v>
+        <v>0.024261</v>
       </c>
       <c r="C8">
-        <v>0.045599</v>
-      </c>
-      <c r="D8">
-        <v>0.02455</v>
-      </c>
-      <c r="E8">
-        <v>0.033029</v>
-      </c>
-      <c r="F8">
-        <v>0.043142</v>
-      </c>
-      <c r="G8">
-        <v>0.050625</v>
+        <v>0.033028</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B9">
-        <v>0.053359</v>
+        <v>0.024792</v>
       </c>
       <c r="C9">
-        <v>0.067115</v>
-      </c>
-      <c r="D9">
-        <v>0.026735</v>
-      </c>
-      <c r="E9">
-        <v>0.034985</v>
-      </c>
-      <c r="F9">
-        <v>0.052919</v>
-      </c>
-      <c r="G9">
-        <v>0.063334</v>
+        <v>0.031977</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B10">
-        <v>0.036949</v>
+        <v>0.029883</v>
       </c>
       <c r="C10">
-        <v>0.046526</v>
-      </c>
-      <c r="D10">
-        <v>0.030516</v>
-      </c>
-      <c r="E10">
-        <v>0.03768</v>
-      </c>
-      <c r="F10">
-        <v>0.052999</v>
-      </c>
-      <c r="G10">
-        <v>0.06417</v>
+        <v>0.036598</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B11">
-        <v>0.033924</v>
+        <v>0.023985</v>
       </c>
       <c r="C11">
-        <v>0.0429</v>
-      </c>
-      <c r="D11">
-        <v>0.023679</v>
-      </c>
-      <c r="E11">
-        <v>0.031466</v>
-      </c>
-      <c r="F11">
-        <v>0.029415</v>
-      </c>
-      <c r="G11">
-        <v>0.037274</v>
+        <v>0.031317</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B12">
-        <v>0.035046</v>
+        <v>0.033504</v>
       </c>
       <c r="C12">
-        <v>0.043553</v>
-      </c>
-      <c r="D12">
-        <v>0.038349</v>
-      </c>
-      <c r="E12">
-        <v>0.047985</v>
-      </c>
-      <c r="F12">
-        <v>0.031261</v>
-      </c>
-      <c r="G12">
-        <v>0.038345</v>
+        <v>0.044083</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B13">
-        <v>0.048273</v>
+        <v>0.029275</v>
       </c>
       <c r="C13">
-        <v>0.06292</v>
-      </c>
-      <c r="D13">
-        <v>0.031016</v>
-      </c>
-      <c r="E13">
-        <v>0.039666</v>
-      </c>
-      <c r="F13">
-        <v>0.047455</v>
-      </c>
-      <c r="G13">
-        <v>0.059505</v>
+        <v>0.036353</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B14">
-        <v>0.027266</v>
+        <v>0.019046</v>
       </c>
       <c r="C14">
-        <v>0.035069</v>
-      </c>
-      <c r="D14">
-        <v>0.018026</v>
-      </c>
-      <c r="E14">
-        <v>0.023116</v>
-      </c>
-      <c r="F14">
-        <v>0.043297</v>
-      </c>
-      <c r="G14">
-        <v>0.051595</v>
+        <v>0.024802</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B15">
-        <v>0.056949</v>
+        <v>0.040624</v>
       </c>
       <c r="C15">
-        <v>0.073864</v>
-      </c>
-      <c r="D15">
-        <v>0.036458</v>
-      </c>
-      <c r="E15">
-        <v>0.050938</v>
-      </c>
-      <c r="F15">
-        <v>0.135624</v>
-      </c>
-      <c r="G15">
-        <v>0.154251</v>
+        <v>0.05349</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B16">
-        <v>0.031566</v>
+        <v>0.029856</v>
       </c>
       <c r="C16">
-        <v>0.038259</v>
-      </c>
-      <c r="D16">
-        <v>0.030046</v>
-      </c>
-      <c r="E16">
-        <v>0.039062</v>
-      </c>
-      <c r="F16">
-        <v>0.035355</v>
-      </c>
-      <c r="G16">
-        <v>0.042579</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
+        <v>0.038592</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B17">
-        <f t="shared" ref="B17:G17" si="0">AVERAGE(B3:B16)</f>
-        <v>0.0454478571428571</v>
+        <f xml:space="preserve">AVERAGE(B3:B16)</f>
+        <v>0.0300037857142857</v>
       </c>
       <c r="C17">
-        <f t="shared" si="0"/>
-        <v>0.0589488571428572</v>
-      </c>
-      <c r="D17">
-        <f t="shared" si="0"/>
-        <v>0.0301353571428571</v>
-      </c>
-      <c r="E17">
-        <f t="shared" si="0"/>
-        <v>0.0389842857142857</v>
-      </c>
-      <c r="F17">
-        <f t="shared" si="0"/>
-        <v>0.0526004285714286</v>
-      </c>
-      <c r="G17">
-        <f t="shared" si="0"/>
-        <v>0.0622043571428572</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
+        <f xml:space="preserve">AVERAGE(C3:C16)</f>
+        <v>0.0383799285714286</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
       <c r="A21" s="2"/>
     </row>
   </sheetData>
